--- a/Messages.xlsx
+++ b/Messages.xlsx
@@ -421,10 +421,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>15.06.2026, 19:19:34</v>
+        <v>15.06.2026, 20:03:46</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>ID-026575</v>
       </c>
       <c r="C2" t="str">
         <v>Іван</v>
@@ -436,78 +436,78 @@
         <v>0674708721</v>
       </c>
       <c r="F2" t="str">
-        <v>питання 1</v>
+        <v>питання 36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15.06.2026, 19:24:24</v>
+        <v>15.06.2026, 20:05:08</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>ID-108376</v>
       </c>
       <c r="C3" t="str">
-        <v>Іван</v>
+        <v>Віталій</v>
       </c>
       <c r="D3" t="str">
-        <v>Умань</v>
+        <v>Гайворон</v>
       </c>
       <c r="E3" t="str">
         <v>0674708721</v>
       </c>
       <c r="F3" t="str">
-        <v>питання 33</v>
+        <v>питання37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>15.06.2026, 19:25:59</v>
+        <v>15.06.2026, 20:15:34</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>ID-734889</v>
       </c>
       <c r="C4" t="str">
-        <v>Іван</v>
+        <v>Олександр</v>
       </c>
       <c r="D4" t="str">
-        <v>Умань</v>
+        <v>Катеринопіль</v>
       </c>
       <c r="E4" t="str">
         <v>0674708721</v>
       </c>
       <c r="F4" t="str">
-        <v>питання 34</v>
+        <v>питання 38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>15.06.2026, 20:00:06</v>
+        <v>15.06.2026, 20:20:25</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>ID-025197</v>
       </c>
       <c r="C5" t="str">
         <v>Іван</v>
       </c>
       <c r="D5" t="str">
-        <v>умань</v>
+        <v>Умань</v>
       </c>
       <c r="E5" t="str">
         <v>0674708721</v>
       </c>
       <c r="F5" t="str">
-        <v>питання 35</v>
+        <v>Питання 39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>15.06.2026, 20:03:46</v>
+        <v>16.06.2026, 07:14:59</v>
       </c>
       <c r="B6" t="str">
-        <v>ID-026575</v>
+        <v>ID-299447</v>
       </c>
       <c r="C6" t="str">
-        <v>Іван</v>
+        <v>test 16-06-2026</v>
       </c>
       <c r="D6" t="str">
         <v>Умань</v>
@@ -516,27 +516,27 @@
         <v>0674708721</v>
       </c>
       <c r="F6" t="str">
-        <v>питання 36</v>
+        <v>питання 41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>15.06.2026, 20:05:08</v>
+        <v>16.06.2026, 07:20:05</v>
       </c>
       <c r="B7" t="str">
-        <v>ID-108376</v>
+        <v>ID-605433</v>
       </c>
       <c r="C7" t="str">
-        <v>Віталій</v>
+        <v>test 2</v>
       </c>
       <c r="D7" t="str">
-        <v>Гайворон</v>
+        <v>Умань</v>
       </c>
       <c r="E7" t="str">
         <v>0674708721</v>
       </c>
       <c r="F7" t="str">
-        <v>питання37</v>
+        <v>питання 42</v>
       </c>
     </row>
   </sheetData>

--- a/Messages.xlsx
+++ b/Messages.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -539,10 +539,110 @@
         <v>питання 42</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>16.06.2026, 09:32:02</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ID-522081</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Сергій</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Умань</v>
+      </c>
+      <c r="E8" t="str">
+        <v>0675630794</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Потрібна металочерепиця</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>16.06.2026, 09:36:27</v>
+      </c>
+      <c r="B9" t="str">
+        <v>ID-787756</v>
+      </c>
+      <c r="C9" t="str">
+        <v>іван</v>
+      </c>
+      <c r="D9" t="str">
+        <v>умань</v>
+      </c>
+      <c r="E9" t="str">
+        <v>0674708721</v>
+      </c>
+      <c r="F9" t="str">
+        <v>питання 54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>16.06.2026, 10:23:10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ID-590458</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Анатолій</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Родниківка</v>
+      </c>
+      <c r="E10" t="str">
+        <v>0674705842</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Додаток</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>16.06.2026, 15:30:56</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ID-056445</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Валентина</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Умань</v>
+      </c>
+      <c r="E11" t="str">
+        <v>0681700171</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Хочу їхати</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>16.06.2026, 17:32:14</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ID-334564</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Uman</v>
+      </c>
+      <c r="E12" t="str">
+        <v>0674708721</v>
+      </c>
+      <c r="F12" t="str">
+        <v>test</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>